--- a/output/Data and Chart Outputs/india_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/india_power_capacity.xlsx
@@ -791,7 +791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -814,42 +814,49 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Monthly: installed capacity, MW, all India (utilities), as on the last day of the month (row dated the 1st). Coal = coal + lignite; Gas; Oil = diesel; Nuclear; Hydro = large hydro (CEA 'Hydro', &gt;25 MW) + small hydro (MNRE, &lt;=25 MW); Wind; Solar (ground-mounted, rooftop and off-grid solar as MNRE reports it); Bioenergy = biomass/bagasse cogeneration + waste to energy; Other = any RES not covered by the break-up. Total_MW = sum of fuels; Grand_total_reported_MW = CEA's own grand total (a check). Detail columns split hydro and show lignite and waste to energy.</t>
+          <t>Monthly: installed capacity, MW, all India (utilities), as on the last day of the month (row dated the 1st). Coal = coal + lignite; Gas; Oil = diesel; Nuclear; Hydro = large hydro (CEA 'Hydro', &gt;25 MW) + small hydro (MNRE, &lt;=25 MW); Wind; Solar (ground-mounted, rooftop and off-grid solar as MNRE reports it); Bioenergy = biomass/bagasse cogeneration + waste to energy; Other = any RES not covered by the break-up. Total_MW = sum of fuels; Grand_total_reported_MW = CEA's own grand total (a check). Detail columns split hydro and show lignite and waste to energy. Lignite_MW is blank before Dec 2021: earlier reports have no lignite column (lignite is inside coal there, so Coal_MW is consistent throughout).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Mar 2025: CEA's report drops gas by 5.06 GW (25,188 -&gt; 20,132 MW), coal by 2.8 GW and nuclear by 0.1 GW while solar / wind / hydro grow, so the total falls 2.6 GW. This is CEA's own revision (retired / de-rated units taken out), not a parse error: every month's fuel sum equals CEA's reported grand total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Files: the NPP file read for each month and its Last-Modified date.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>COVERAGE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Monthly from Jan 2019 to Aug 2026. Utilities only (captive plants are not included). Renewable capacity is MNRE's figure as carried in CEA's report. A month's report appears on NPP about 2-3 weeks after the month ends.</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CEA (Central Electricity Authority, Ministry of Power), All India Installed Capacity (Utilities) monthly report, via the National Power Portal: https://npp.gov.in/publishedReports (files https://npp.gov.in/public-reports/cea/monthly/installcap/YYYY/MON/capacity1-YYYY-MM.xls); also published at https://cea.nic.in/installed-capacity-report/?lang=en.</t>
         </is>
@@ -3028,9 +3035,6 @@
       <c r="M2" t="n">
         <v>4517.4</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
         <v>138.3</v>
       </c>
@@ -3078,9 +3082,6 @@
       <c r="M3" t="n">
         <v>4528</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
         <v>138.3</v>
       </c>
@@ -3128,9 +3129,6 @@
       <c r="M4" t="n">
         <v>4593.2</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
         <v>138.3</v>
       </c>
@@ -3178,9 +3176,6 @@
       <c r="M5" t="n">
         <v>4593.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>138.3</v>
       </c>
@@ -3228,9 +3223,6 @@
       <c r="M6" t="n">
         <v>4594.2</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
       <c r="O6" t="n">
         <v>138.3</v>
       </c>
@@ -3278,9 +3270,6 @@
       <c r="M7" t="n">
         <v>4604.8</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
         <v>138.3</v>
       </c>
@@ -3328,9 +3317,6 @@
       <c r="M8" t="n">
         <v>4604.8</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
       <c r="O8" t="n">
         <v>138.3</v>
       </c>
@@ -3378,9 +3364,6 @@
       <c r="M9" t="n">
         <v>4608.8</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
       <c r="O9" t="n">
         <v>139.8</v>
       </c>
@@ -3428,9 +3411,6 @@
       <c r="M10" t="n">
         <v>4610.8</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
         <v>139.8</v>
       </c>
@@ -3478,9 +3458,6 @@
       <c r="M11" t="n">
         <v>4647.1</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>139.8</v>
       </c>
@@ -3528,9 +3505,6 @@
       <c r="M12" t="n">
         <v>4647.6</v>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" t="n">
         <v>139.8</v>
       </c>
@@ -3578,9 +3552,6 @@
       <c r="M13" t="n">
         <v>4671.6</v>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
       <c r="O13" t="n">
         <v>139.8</v>
       </c>
@@ -3628,9 +3599,6 @@
       <c r="M14" t="n">
         <v>4676.6</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
       <c r="O14" t="n">
         <v>139.8</v>
       </c>
@@ -3678,9 +3646,6 @@
       <c r="M15" t="n">
         <v>4683.2</v>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
       <c r="O15" t="n">
         <v>139.8</v>
       </c>
@@ -3728,9 +3693,6 @@
       <c r="M16" t="n">
         <v>4683.2</v>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
       <c r="O16" t="n">
         <v>147.6</v>
       </c>
@@ -3778,9 +3740,6 @@
       <c r="M17" t="n">
         <v>4683.2</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
       <c r="O17" t="n">
         <v>147.6</v>
       </c>
@@ -3828,9 +3787,6 @@
       <c r="M18" t="n">
         <v>4683.2</v>
       </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
       <c r="O18" t="n">
         <v>148.8</v>
       </c>
@@ -3878,9 +3834,6 @@
       <c r="M19" t="n">
         <v>4688.2</v>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
       <c r="O19" t="n">
         <v>148.8</v>
       </c>
@@ -3928,9 +3881,6 @@
       <c r="M20" t="n">
         <v>4712.2</v>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
       <c r="O20" t="n">
         <v>148.8</v>
       </c>
@@ -3978,9 +3928,6 @@
       <c r="M21" t="n">
         <v>4740</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
       <c r="O21" t="n">
         <v>168.6</v>
       </c>
@@ -4028,9 +3975,6 @@
       <c r="M22" t="n">
         <v>4740</v>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
       <c r="O22" t="n">
         <v>168.6</v>
       </c>
@@ -4078,9 +4022,6 @@
       <c r="M23" t="n">
         <v>4740.5</v>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
       <c r="O23" t="n">
         <v>168.6</v>
       </c>
@@ -4128,9 +4069,6 @@
       <c r="M24" t="n">
         <v>4740.5</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>168.6</v>
       </c>
@@ -4178,9 +4116,6 @@
       <c r="M25" t="n">
         <v>4750.5</v>
       </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
       <c r="O25" t="n">
         <v>168.6</v>
       </c>
@@ -4228,9 +4163,6 @@
       <c r="M26" t="n">
         <v>4758.5</v>
       </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
       <c r="O26" t="n">
         <v>168.6</v>
       </c>
@@ -4278,9 +4210,6 @@
       <c r="M27" t="n">
         <v>4783.1</v>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
       <c r="O27" t="n">
         <v>168.6</v>
       </c>
@@ -4328,9 +4257,6 @@
       <c r="M28" t="n">
         <v>4786.8</v>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="n">
         <v>168.6</v>
       </c>
@@ -4378,9 +4304,6 @@
       <c r="M29" t="n">
         <v>4786.8</v>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
       <c r="O29" t="n">
         <v>168.6</v>
       </c>
@@ -4428,9 +4351,6 @@
       <c r="M30" t="n">
         <v>4786.8</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
       <c r="O30" t="n">
         <v>168.6</v>
       </c>
@@ -4478,9 +4398,6 @@
       <c r="M31" t="n">
         <v>4793.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
       <c r="O31" t="n">
         <v>168.6</v>
       </c>
@@ -4528,9 +4445,6 @@
       <c r="M32" t="n">
         <v>4794.6</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
       <c r="O32" t="n">
         <v>388.2</v>
       </c>
@@ -4578,9 +4492,6 @@
       <c r="M33" t="n">
         <v>4807.8</v>
       </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
       <c r="O33" t="n">
         <v>401.8</v>
       </c>
@@ -4628,9 +4539,6 @@
       <c r="M34" t="n">
         <v>4809.8</v>
       </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
       <c r="O34" t="n">
         <v>401.8</v>
       </c>
@@ -4678,9 +4586,6 @@
       <c r="M35" t="n">
         <v>4821.8</v>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
       <c r="O35" t="n">
         <v>401.8</v>
       </c>
@@ -4727,9 +4632,6 @@
       </c>
       <c r="M36" t="n">
         <v>4831.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>434.1</v>

--- a/output/Data and Chart Outputs/india_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/india_power_capacity.xlsx
@@ -156,7 +156,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>India installed capacity (CEA) (to Aug/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>India installed capacity (CEA) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -186,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$69</f>
+              <f>'Chart'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -214,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$69</f>
+              <f>'Chart'!$C$2:$C$70</f>
             </numRef>
           </val>
         </ser>
@@ -242,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$69</f>
+              <f>'Chart'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -270,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$69</f>
+              <f>'Chart'!$E$2:$E$70</f>
             </numRef>
           </val>
         </ser>
@@ -289,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -298,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$69</f>
+              <f>'Chart'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -317,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -326,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$69</f>
+              <f>'Chart'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -345,7 +346,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -354,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$69</f>
+              <f>'Chart'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -373,7 +374,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -382,12 +383,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
+              <f>'Chart'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$I$2:$I$69</f>
+              <f>'Chart'!$I$2:$I$70</f>
             </numRef>
           </val>
         </ser>
@@ -843,7 +844,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monthly from Jan 2019 to Aug 2026. Utilities only (captive plants are not included). Renewable capacity is MNRE's figure as carried in CEA's report. A month's report appears on NPP about 2-3 weeks after the month ends.</t>
+          <t>Monthly from Jan 2019 to Sep 2026. Utilities only (captive plants are not included). Renewable capacity is MNRE's figure as carried in CEA's report. A month's report appears on NPP about 2-3 weeks after the month ends.</t>
         </is>
       </c>
     </row>
@@ -873,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2895,6 +2896,35 @@
         <v>230.7775</v>
       </c>
       <c r="I69" t="n">
+        <v>8.779999999999999</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57.2464</v>
+      </c>
+      <c r="C70" t="n">
+        <v>19.144</v>
+      </c>
+      <c r="D70" t="n">
+        <v>59.2011</v>
+      </c>
+      <c r="E70" t="n">
+        <v>171.0515</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.2883</v>
+      </c>
+      <c r="G70" t="n">
+        <v>11.7476</v>
+      </c>
+      <c r="H70" t="n">
+        <v>231.4375</v>
+      </c>
+      <c r="I70" t="n">
         <v>8.779999999999999</v>
       </c>
     </row>
@@ -2910,7 +2940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P93"/>
+  <dimension ref="A1:P94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7488,6 +7518,56 @@
       </c>
       <c r="P93" t="n">
         <v>554544.2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57246.4</v>
+      </c>
+      <c r="C94" t="n">
+        <v>19144</v>
+      </c>
+      <c r="D94" t="n">
+        <v>59201.1</v>
+      </c>
+      <c r="E94" t="n">
+        <v>171051.5</v>
+      </c>
+      <c r="F94" t="n">
+        <v>231437.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>8780</v>
+      </c>
+      <c r="H94" t="n">
+        <v>288.3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>11747.6</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>558896.4</v>
+      </c>
+      <c r="L94" t="n">
+        <v>52064.7</v>
+      </c>
+      <c r="M94" t="n">
+        <v>5181.8</v>
+      </c>
+      <c r="N94" t="n">
+        <v>6370</v>
+      </c>
+      <c r="O94" t="n">
+        <v>878.4</v>
+      </c>
+      <c r="P94" t="n">
+        <v>558896.4</v>
       </c>
     </row>
   </sheetData>
@@ -7501,7 +7581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8901,6 +8981,21 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://npp.gov.in/public-reports/cea/monthly/installcap/2026/SEP/capacity1-2026-09.xls</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Mon, 19 Oct 2026 14:46:15 GMT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/india_power_capacity.xlsx
+++ b/output/Data and Chart Outputs/india_power_capacity.xlsx
@@ -21,8 +21,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -62,12 +62,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -833,7 +834,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
@@ -848,7 +848,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -928,7 +927,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -957,7 +956,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -986,7 +985,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -1015,7 +1014,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -1044,7 +1043,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -1073,7 +1072,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -1102,7 +1101,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -1131,7 +1130,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -1160,7 +1159,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -1189,7 +1188,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -1218,7 +1217,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -1247,7 +1246,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -1276,7 +1275,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -1334,7 +1333,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -1363,7 +1362,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -1392,7 +1391,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -1421,7 +1420,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -1450,7 +1449,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -1479,7 +1478,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -1508,7 +1507,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -1537,7 +1536,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -1566,7 +1565,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -1595,7 +1594,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -1624,7 +1623,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -1653,7 +1652,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -1682,7 +1681,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -1711,7 +1710,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -1740,7 +1739,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -1769,7 +1768,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -1798,7 +1797,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -1827,7 +1826,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -1856,7 +1855,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -1885,7 +1884,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -1914,7 +1913,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -1943,7 +1942,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -1972,7 +1971,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -2001,7 +2000,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -2030,7 +2029,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -2059,7 +2058,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -2088,7 +2087,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -2117,7 +2116,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -2146,7 +2145,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -2175,7 +2174,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -2204,7 +2203,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -2233,7 +2232,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -2262,7 +2261,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -2291,7 +2290,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -2320,7 +2319,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -2349,7 +2348,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -2378,7 +2377,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -2407,7 +2406,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -2436,7 +2435,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -2465,7 +2464,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -2494,7 +2493,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -2523,7 +2522,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -2552,7 +2551,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -2581,7 +2580,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -2610,7 +2609,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -2639,7 +2638,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -2668,7 +2667,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -2697,7 +2696,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -2726,7 +2725,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -2755,7 +2754,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -2784,7 +2783,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -2813,7 +2812,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">
@@ -2842,7 +2841,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B68" t="n">
@@ -2871,7 +2870,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B69" t="n">
@@ -2900,7 +2899,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B70" t="n">
